--- a/2025/battwatts_sensitivity/battwatts_sensitivity_outputs_shade_todiscuss.xlsx
+++ b/2025/battwatts_sensitivity/battwatts_sensitivity_outputs_shade_todiscuss.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bspeetle/Desktop/repo/SAM-analyses/2025/battwatts_sensitivity/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{C0B2E66D-17D5-E84B-A849-FD5ED3D275E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{6D0452CB-E66F-2D44-892E-9BF9C03B8251}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="580" yWindow="760" windowWidth="33980" windowHeight="20040" xr2:uid="{88777FE6-FCBD-8240-B1A6-FED69E4F09BD}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="407" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="140">
   <si>
     <t>state_long</t>
   </si>
@@ -447,6 +447,12 @@
   </si>
   <si>
     <t>193.44050203618923</t>
+  </si>
+  <si>
+    <t>difference between 3d shade and annual loss method - PV only</t>
+  </si>
+  <si>
+    <t>difference between 3d shade and annual loss method - PV+BESS</t>
   </si>
 </sst>
 </file>
@@ -1334,6 +1340,8 @@
     <col min="17" max="17" width="30.6640625" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="31.1640625" hidden="1" customWidth="1"/>
     <col min="19" max="19" width="28.1640625" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="51.5" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="53.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.2">
@@ -1393,6 +1401,12 @@
       </c>
       <c r="S1" t="s">
         <v>18</v>
+      </c>
+      <c r="U1" t="s">
+        <v>138</v>
+      </c>
+      <c r="V1" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.2">
